--- a/src/main/resources/static/Template_import_asset_night_10_7.xlsx
+++ b/src/main/resources/static/Template_import_asset_night_10_7.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hieux\Desktop\Projects\src\main\resources\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D84FCE1F-3BDD-433C-B67C-B178540B4295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3A983A-AE24-4A3E-A107-7B5D43B09E57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ImportAsset" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -906,6 +907,51 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -919,9 +965,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1001,48 +1044,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="21" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1371,380 +1372,380 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:147" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
-      <c r="N1" s="41"/>
-      <c r="O1" s="41"/>
-      <c r="P1" s="41"/>
-      <c r="Q1" s="42"/>
-      <c r="R1" s="75" t="s">
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
+      <c r="M1" s="55"/>
+      <c r="N1" s="55"/>
+      <c r="O1" s="55"/>
+      <c r="P1" s="55"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="S1" s="76"/>
-      <c r="T1" s="76"/>
-      <c r="U1" s="76"/>
-      <c r="V1" s="76"/>
-      <c r="W1" s="76"/>
-      <c r="X1" s="76"/>
-      <c r="Y1" s="76"/>
-      <c r="Z1" s="76"/>
-      <c r="AA1" s="76"/>
-      <c r="AB1" s="76"/>
-      <c r="AC1" s="76"/>
-      <c r="AD1" s="76"/>
-      <c r="AE1" s="76"/>
-      <c r="AF1" s="76"/>
-      <c r="AG1" s="76"/>
-      <c r="AH1" s="76"/>
-      <c r="AI1" s="76"/>
-      <c r="AJ1" s="76"/>
-      <c r="AK1" s="76"/>
-      <c r="AL1" s="76"/>
-      <c r="AM1" s="76"/>
-      <c r="AN1" s="76"/>
-      <c r="AO1" s="76"/>
-      <c r="AP1" s="76"/>
-      <c r="AQ1" s="76"/>
-      <c r="AR1" s="76"/>
-      <c r="AS1" s="76"/>
-      <c r="AT1" s="76"/>
-      <c r="AU1" s="76"/>
-      <c r="AV1" s="76"/>
-      <c r="AW1" s="76"/>
-      <c r="AX1" s="76"/>
-      <c r="AY1" s="76"/>
-      <c r="AZ1" s="76"/>
-      <c r="BA1" s="76"/>
-      <c r="BB1" s="76"/>
-      <c r="BC1" s="76"/>
-      <c r="BD1" s="76"/>
-      <c r="BE1" s="76"/>
-      <c r="BF1" s="76"/>
-      <c r="BG1" s="76"/>
-      <c r="BH1" s="76"/>
-      <c r="BI1" s="76"/>
-      <c r="BJ1" s="76"/>
-      <c r="BK1" s="76"/>
-      <c r="BL1" s="76"/>
-      <c r="BM1" s="76"/>
-      <c r="BN1" s="76"/>
-      <c r="BO1" s="76"/>
-      <c r="BP1" s="76"/>
-      <c r="BQ1" s="76"/>
-      <c r="BR1" s="76"/>
-      <c r="BS1" s="76"/>
-      <c r="BT1" s="76"/>
-      <c r="BU1" s="76"/>
-      <c r="BV1" s="76"/>
-      <c r="BW1" s="76"/>
-      <c r="BX1" s="76"/>
-      <c r="BY1" s="76"/>
-      <c r="BZ1" s="76"/>
-      <c r="CA1" s="76"/>
-      <c r="CB1" s="76"/>
-      <c r="CC1" s="76"/>
-      <c r="CD1" s="76"/>
-      <c r="CE1" s="76"/>
-      <c r="CF1" s="76"/>
-      <c r="CG1" s="76"/>
-      <c r="CH1" s="76"/>
-      <c r="CI1" s="76"/>
-      <c r="CJ1" s="76"/>
-      <c r="CK1" s="76"/>
-      <c r="CL1" s="76"/>
-      <c r="CM1" s="76"/>
-      <c r="CN1" s="76"/>
-      <c r="CO1" s="76"/>
-      <c r="CP1" s="77"/>
-      <c r="CQ1" s="56" t="s">
+      <c r="S1" s="34"/>
+      <c r="T1" s="34"/>
+      <c r="U1" s="34"/>
+      <c r="V1" s="34"/>
+      <c r="W1" s="34"/>
+      <c r="X1" s="34"/>
+      <c r="Y1" s="34"/>
+      <c r="Z1" s="34"/>
+      <c r="AA1" s="34"/>
+      <c r="AB1" s="34"/>
+      <c r="AC1" s="34"/>
+      <c r="AD1" s="34"/>
+      <c r="AE1" s="34"/>
+      <c r="AF1" s="34"/>
+      <c r="AG1" s="34"/>
+      <c r="AH1" s="34"/>
+      <c r="AI1" s="34"/>
+      <c r="AJ1" s="34"/>
+      <c r="AK1" s="34"/>
+      <c r="AL1" s="34"/>
+      <c r="AM1" s="34"/>
+      <c r="AN1" s="34"/>
+      <c r="AO1" s="34"/>
+      <c r="AP1" s="34"/>
+      <c r="AQ1" s="34"/>
+      <c r="AR1" s="34"/>
+      <c r="AS1" s="34"/>
+      <c r="AT1" s="34"/>
+      <c r="AU1" s="34"/>
+      <c r="AV1" s="34"/>
+      <c r="AW1" s="34"/>
+      <c r="AX1" s="34"/>
+      <c r="AY1" s="34"/>
+      <c r="AZ1" s="34"/>
+      <c r="BA1" s="34"/>
+      <c r="BB1" s="34"/>
+      <c r="BC1" s="34"/>
+      <c r="BD1" s="34"/>
+      <c r="BE1" s="34"/>
+      <c r="BF1" s="34"/>
+      <c r="BG1" s="34"/>
+      <c r="BH1" s="34"/>
+      <c r="BI1" s="34"/>
+      <c r="BJ1" s="34"/>
+      <c r="BK1" s="34"/>
+      <c r="BL1" s="34"/>
+      <c r="BM1" s="34"/>
+      <c r="BN1" s="34"/>
+      <c r="BO1" s="34"/>
+      <c r="BP1" s="34"/>
+      <c r="BQ1" s="34"/>
+      <c r="BR1" s="34"/>
+      <c r="BS1" s="34"/>
+      <c r="BT1" s="34"/>
+      <c r="BU1" s="34"/>
+      <c r="BV1" s="34"/>
+      <c r="BW1" s="34"/>
+      <c r="BX1" s="34"/>
+      <c r="BY1" s="34"/>
+      <c r="BZ1" s="34"/>
+      <c r="CA1" s="34"/>
+      <c r="CB1" s="34"/>
+      <c r="CC1" s="34"/>
+      <c r="CD1" s="34"/>
+      <c r="CE1" s="34"/>
+      <c r="CF1" s="34"/>
+      <c r="CG1" s="34"/>
+      <c r="CH1" s="34"/>
+      <c r="CI1" s="34"/>
+      <c r="CJ1" s="34"/>
+      <c r="CK1" s="34"/>
+      <c r="CL1" s="34"/>
+      <c r="CM1" s="34"/>
+      <c r="CN1" s="34"/>
+      <c r="CO1" s="34"/>
+      <c r="CP1" s="35"/>
+      <c r="CQ1" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="CR1" s="57"/>
-      <c r="CS1" s="57"/>
-      <c r="CT1" s="57"/>
-      <c r="CU1" s="57"/>
-      <c r="CV1" s="57"/>
-      <c r="CW1" s="57"/>
-      <c r="CX1" s="58"/>
-      <c r="CY1" s="47" t="s">
+      <c r="CR1" s="71"/>
+      <c r="CS1" s="71"/>
+      <c r="CT1" s="71"/>
+      <c r="CU1" s="71"/>
+      <c r="CV1" s="71"/>
+      <c r="CW1" s="71"/>
+      <c r="CX1" s="72"/>
+      <c r="CY1" s="61" t="s">
         <v>75</v>
       </c>
-      <c r="CZ1" s="48"/>
-      <c r="DA1" s="48"/>
-      <c r="DB1" s="48"/>
-      <c r="DC1" s="48"/>
-      <c r="DD1" s="48"/>
-      <c r="DE1" s="48"/>
-      <c r="DF1" s="48"/>
-      <c r="DG1" s="48"/>
-      <c r="DH1" s="48"/>
-      <c r="DI1" s="48"/>
-      <c r="DJ1" s="48"/>
-      <c r="DK1" s="48"/>
-      <c r="DL1" s="48"/>
-      <c r="DM1" s="48"/>
-      <c r="DN1" s="48"/>
-      <c r="DO1" s="48"/>
-      <c r="DP1" s="48"/>
-      <c r="DQ1" s="48"/>
-      <c r="DR1" s="48"/>
-      <c r="DS1" s="48"/>
-      <c r="DT1" s="48"/>
-      <c r="DU1" s="48"/>
-      <c r="DV1" s="48"/>
-      <c r="DW1" s="48"/>
-      <c r="DX1" s="48"/>
-      <c r="DY1" s="48"/>
-      <c r="DZ1" s="48"/>
-      <c r="EA1" s="48"/>
-      <c r="EB1" s="49"/>
-      <c r="EC1" s="39" t="s">
+      <c r="CZ1" s="62"/>
+      <c r="DA1" s="62"/>
+      <c r="DB1" s="62"/>
+      <c r="DC1" s="62"/>
+      <c r="DD1" s="62"/>
+      <c r="DE1" s="62"/>
+      <c r="DF1" s="62"/>
+      <c r="DG1" s="62"/>
+      <c r="DH1" s="62"/>
+      <c r="DI1" s="62"/>
+      <c r="DJ1" s="62"/>
+      <c r="DK1" s="62"/>
+      <c r="DL1" s="62"/>
+      <c r="DM1" s="62"/>
+      <c r="DN1" s="62"/>
+      <c r="DO1" s="62"/>
+      <c r="DP1" s="62"/>
+      <c r="DQ1" s="62"/>
+      <c r="DR1" s="62"/>
+      <c r="DS1" s="62"/>
+      <c r="DT1" s="62"/>
+      <c r="DU1" s="62"/>
+      <c r="DV1" s="62"/>
+      <c r="DW1" s="62"/>
+      <c r="DX1" s="62"/>
+      <c r="DY1" s="62"/>
+      <c r="DZ1" s="62"/>
+      <c r="EA1" s="62"/>
+      <c r="EB1" s="63"/>
+      <c r="EC1" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="ED1" s="39"/>
-      <c r="EE1" s="39"/>
-      <c r="EF1" s="39"/>
-      <c r="EG1" s="39"/>
-      <c r="EH1" s="39"/>
-      <c r="EI1" s="39"/>
-      <c r="EJ1" s="39"/>
-      <c r="EK1" s="39"/>
-      <c r="EL1" s="39"/>
-      <c r="EM1" s="39"/>
-      <c r="EN1" s="39"/>
-      <c r="EO1" s="39"/>
-      <c r="EP1" s="39"/>
-      <c r="EQ1" s="39"/>
+      <c r="ED1" s="53"/>
+      <c r="EE1" s="53"/>
+      <c r="EF1" s="53"/>
+      <c r="EG1" s="53"/>
+      <c r="EH1" s="53"/>
+      <c r="EI1" s="53"/>
+      <c r="EJ1" s="53"/>
+      <c r="EK1" s="53"/>
+      <c r="EL1" s="53"/>
+      <c r="EM1" s="53"/>
+      <c r="EN1" s="53"/>
+      <c r="EO1" s="53"/>
+      <c r="EP1" s="53"/>
+      <c r="EQ1" s="53"/>
     </row>
     <row r="2" spans="1:147" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="70" t="s">
+      <c r="A2" s="43" t="s">
         <v>69</v>
       </c>
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="42" t="s">
         <v>122</v>
       </c>
-      <c r="D2" s="70" t="s">
+      <c r="D2" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="E2" s="70" t="s">
+      <c r="E2" s="43" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="70" t="s">
+      <c r="F2" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="G2" s="70" t="s">
+      <c r="G2" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="70" t="s">
+      <c r="H2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="35" t="s">
+      <c r="I2" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="J2" s="36"/>
-      <c r="K2" s="32" t="s">
+      <c r="J2" s="51"/>
+      <c r="K2" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="L2" s="33"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="70" t="s">
+      <c r="L2" s="48"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="37" t="s">
+      <c r="O2" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="37" t="s">
+      <c r="P2" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="37" t="s">
+      <c r="Q2" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="R2" s="43" t="s">
+      <c r="R2" s="57" t="s">
         <v>76</v>
       </c>
-      <c r="S2" s="43"/>
-      <c r="T2" s="43"/>
-      <c r="U2" s="43"/>
-      <c r="V2" s="43"/>
-      <c r="W2" s="43"/>
-      <c r="X2" s="43"/>
-      <c r="Y2" s="73" t="s">
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="57"/>
+      <c r="V2" s="57"/>
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
+      <c r="Y2" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="Z2" s="73"/>
-      <c r="AA2" s="73"/>
-      <c r="AB2" s="73"/>
-      <c r="AC2" s="74" t="s">
+      <c r="Z2" s="46"/>
+      <c r="AA2" s="46"/>
+      <c r="AB2" s="46"/>
+      <c r="AC2" s="32" t="s">
         <v>23</v>
       </c>
-      <c r="AD2" s="74"/>
-      <c r="AE2" s="74"/>
-      <c r="AF2" s="74"/>
-      <c r="AG2" s="74"/>
-      <c r="AH2" s="74"/>
-      <c r="AI2" s="74"/>
-      <c r="AJ2" s="74"/>
-      <c r="AK2" s="74"/>
-      <c r="AL2" s="71" t="s">
+      <c r="AD2" s="32"/>
+      <c r="AE2" s="32"/>
+      <c r="AF2" s="32"/>
+      <c r="AG2" s="32"/>
+      <c r="AH2" s="32"/>
+      <c r="AI2" s="32"/>
+      <c r="AJ2" s="32"/>
+      <c r="AK2" s="32"/>
+      <c r="AL2" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="AM2" s="71"/>
-      <c r="AN2" s="71"/>
-      <c r="AO2" s="71"/>
-      <c r="AP2" s="71"/>
-      <c r="AQ2" s="71"/>
-      <c r="AR2" s="72" t="s">
+      <c r="AM2" s="44"/>
+      <c r="AN2" s="44"/>
+      <c r="AO2" s="44"/>
+      <c r="AP2" s="44"/>
+      <c r="AQ2" s="44"/>
+      <c r="AR2" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="AS2" s="72"/>
-      <c r="AT2" s="72"/>
-      <c r="AU2" s="72"/>
-      <c r="AV2" s="72"/>
-      <c r="AW2" s="72"/>
-      <c r="AX2" s="72"/>
-      <c r="AY2" s="72"/>
-      <c r="AZ2" s="72"/>
-      <c r="BA2" s="72"/>
-      <c r="BB2" s="72"/>
-      <c r="BC2" s="72"/>
-      <c r="BD2" s="72"/>
-      <c r="BE2" s="72"/>
-      <c r="BF2" s="72"/>
-      <c r="BG2" s="72"/>
-      <c r="BH2" s="72"/>
-      <c r="BI2" s="72"/>
-      <c r="BJ2" s="72"/>
-      <c r="BK2" s="72"/>
-      <c r="BL2" s="72"/>
-      <c r="BM2" s="72"/>
-      <c r="BN2" s="72"/>
-      <c r="BO2" s="44" t="s">
+      <c r="AS2" s="45"/>
+      <c r="AT2" s="45"/>
+      <c r="AU2" s="45"/>
+      <c r="AV2" s="45"/>
+      <c r="AW2" s="45"/>
+      <c r="AX2" s="45"/>
+      <c r="AY2" s="45"/>
+      <c r="AZ2" s="45"/>
+      <c r="BA2" s="45"/>
+      <c r="BB2" s="45"/>
+      <c r="BC2" s="45"/>
+      <c r="BD2" s="45"/>
+      <c r="BE2" s="45"/>
+      <c r="BF2" s="45"/>
+      <c r="BG2" s="45"/>
+      <c r="BH2" s="45"/>
+      <c r="BI2" s="45"/>
+      <c r="BJ2" s="45"/>
+      <c r="BK2" s="45"/>
+      <c r="BL2" s="45"/>
+      <c r="BM2" s="45"/>
+      <c r="BN2" s="45"/>
+      <c r="BO2" s="58" t="s">
         <v>41</v>
       </c>
-      <c r="BP2" s="44"/>
-      <c r="BQ2" s="44"/>
-      <c r="BR2" s="44"/>
-      <c r="BS2" s="44"/>
-      <c r="BT2" s="44"/>
-      <c r="BU2" s="44"/>
-      <c r="BV2" s="44"/>
-      <c r="BW2" s="44"/>
-      <c r="BX2" s="44"/>
-      <c r="BY2" s="44"/>
-      <c r="BZ2" s="44"/>
-      <c r="CA2" s="44"/>
-      <c r="CB2" s="44"/>
-      <c r="CC2" s="44"/>
-      <c r="CD2" s="44"/>
-      <c r="CE2" s="44"/>
-      <c r="CF2" s="44"/>
-      <c r="CG2" s="45" t="s">
+      <c r="BP2" s="58"/>
+      <c r="BQ2" s="58"/>
+      <c r="BR2" s="58"/>
+      <c r="BS2" s="58"/>
+      <c r="BT2" s="58"/>
+      <c r="BU2" s="58"/>
+      <c r="BV2" s="58"/>
+      <c r="BW2" s="58"/>
+      <c r="BX2" s="58"/>
+      <c r="BY2" s="58"/>
+      <c r="BZ2" s="58"/>
+      <c r="CA2" s="58"/>
+      <c r="CB2" s="58"/>
+      <c r="CC2" s="58"/>
+      <c r="CD2" s="58"/>
+      <c r="CE2" s="58"/>
+      <c r="CF2" s="58"/>
+      <c r="CG2" s="59" t="s">
         <v>43</v>
       </c>
-      <c r="CH2" s="45"/>
-      <c r="CI2" s="45"/>
-      <c r="CJ2" s="43" t="s">
+      <c r="CH2" s="59"/>
+      <c r="CI2" s="59"/>
+      <c r="CJ2" s="57" t="s">
         <v>77</v>
       </c>
-      <c r="CK2" s="43"/>
-      <c r="CL2" s="43"/>
-      <c r="CM2" s="43"/>
-      <c r="CN2" s="43"/>
-      <c r="CO2" s="43"/>
-      <c r="CP2" s="43"/>
-      <c r="CQ2" s="59"/>
-      <c r="CR2" s="60"/>
-      <c r="CS2" s="60"/>
-      <c r="CT2" s="60"/>
-      <c r="CU2" s="60"/>
-      <c r="CV2" s="60"/>
-      <c r="CW2" s="60"/>
-      <c r="CX2" s="61"/>
-      <c r="CY2" s="62" t="s">
+      <c r="CK2" s="57"/>
+      <c r="CL2" s="57"/>
+      <c r="CM2" s="57"/>
+      <c r="CN2" s="57"/>
+      <c r="CO2" s="57"/>
+      <c r="CP2" s="57"/>
+      <c r="CQ2" s="73"/>
+      <c r="CR2" s="74"/>
+      <c r="CS2" s="74"/>
+      <c r="CT2" s="74"/>
+      <c r="CU2" s="74"/>
+      <c r="CV2" s="74"/>
+      <c r="CW2" s="74"/>
+      <c r="CX2" s="75"/>
+      <c r="CY2" s="76" t="s">
         <v>89</v>
       </c>
-      <c r="CZ2" s="53" t="s">
+      <c r="CZ2" s="67" t="s">
         <v>78</v>
       </c>
-      <c r="DA2" s="54"/>
-      <c r="DB2" s="54"/>
-      <c r="DC2" s="54"/>
-      <c r="DD2" s="54"/>
-      <c r="DE2" s="55"/>
-      <c r="DF2" s="46" t="s">
+      <c r="DA2" s="68"/>
+      <c r="DB2" s="68"/>
+      <c r="DC2" s="68"/>
+      <c r="DD2" s="68"/>
+      <c r="DE2" s="69"/>
+      <c r="DF2" s="60" t="s">
         <v>90</v>
       </c>
-      <c r="DG2" s="46"/>
-      <c r="DH2" s="46"/>
-      <c r="DI2" s="46"/>
-      <c r="DJ2" s="46"/>
-      <c r="DK2" s="46"/>
-      <c r="DL2" s="46"/>
-      <c r="DM2" s="46"/>
-      <c r="DN2" s="46"/>
-      <c r="DO2" s="46"/>
-      <c r="DP2" s="46"/>
-      <c r="DQ2" s="50" t="s">
+      <c r="DG2" s="60"/>
+      <c r="DH2" s="60"/>
+      <c r="DI2" s="60"/>
+      <c r="DJ2" s="60"/>
+      <c r="DK2" s="60"/>
+      <c r="DL2" s="60"/>
+      <c r="DM2" s="60"/>
+      <c r="DN2" s="60"/>
+      <c r="DO2" s="60"/>
+      <c r="DP2" s="60"/>
+      <c r="DQ2" s="64" t="s">
         <v>97</v>
       </c>
-      <c r="DR2" s="51"/>
-      <c r="DS2" s="51"/>
-      <c r="DT2" s="51"/>
-      <c r="DU2" s="51"/>
-      <c r="DV2" s="51"/>
-      <c r="DW2" s="51"/>
-      <c r="DX2" s="51"/>
-      <c r="DY2" s="51"/>
-      <c r="DZ2" s="51"/>
-      <c r="EA2" s="51"/>
-      <c r="EB2" s="52"/>
+      <c r="DR2" s="65"/>
+      <c r="DS2" s="65"/>
+      <c r="DT2" s="65"/>
+      <c r="DU2" s="65"/>
+      <c r="DV2" s="65"/>
+      <c r="DW2" s="65"/>
+      <c r="DX2" s="65"/>
+      <c r="DY2" s="65"/>
+      <c r="DZ2" s="65"/>
+      <c r="EA2" s="65"/>
+      <c r="EB2" s="66"/>
       <c r="EC2" s="2"/>
       <c r="ED2" s="2"/>
       <c r="EE2" s="2"/>
       <c r="EF2" s="2"/>
-      <c r="EG2" s="67" t="s">
+      <c r="EG2" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="EH2" s="68"/>
-      <c r="EI2" s="68"/>
-      <c r="EJ2" s="69"/>
-      <c r="EK2" s="64" t="s">
+      <c r="EH2" s="40"/>
+      <c r="EI2" s="40"/>
+      <c r="EJ2" s="41"/>
+      <c r="EK2" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="EL2" s="65"/>
-      <c r="EM2" s="65"/>
-      <c r="EN2" s="65"/>
-      <c r="EO2" s="66"/>
-      <c r="EP2" s="38" t="s">
+      <c r="EL2" s="37"/>
+      <c r="EM2" s="37"/>
+      <c r="EN2" s="37"/>
+      <c r="EO2" s="38"/>
+      <c r="EP2" s="52" t="s">
         <v>113</v>
       </c>
-      <c r="EQ2" s="38"/>
+      <c r="EQ2" s="52"/>
     </row>
     <row r="3" spans="1:147" ht="90" x14ac:dyDescent="0.25">
-      <c r="A3" s="37"/>
-      <c r="B3" s="37"/>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37"/>
-      <c r="H3" s="37"/>
+      <c r="A3" s="42"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
       <c r="I3" s="8" t="s">
         <v>1</v>
       </c>
@@ -1760,10 +1761,10 @@
       <c r="M3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
       <c r="R3" s="17" t="s">
         <v>12</v>
       </c>
@@ -2019,7 +2020,7 @@
       <c r="CX3" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="CY3" s="63"/>
+      <c r="CY3" s="77"/>
       <c r="CZ3" s="9" t="s">
         <v>51</v>
       </c>
@@ -2219,26 +2220,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="AC2:AK2"/>
-    <mergeCell ref="R1:CP1"/>
-    <mergeCell ref="EK2:EO2"/>
-    <mergeCell ref="EG2:EJ2"/>
-    <mergeCell ref="Q2:Q3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="N2:N3"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="AL2:AQ2"/>
-    <mergeCell ref="AR2:BN2"/>
-    <mergeCell ref="Y2:AB2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="I2:J2"/>
     <mergeCell ref="P2:P3"/>
     <mergeCell ref="EP2:EQ2"/>
     <mergeCell ref="EC1:EQ1"/>
@@ -2253,9 +2234,29 @@
     <mergeCell ref="CZ2:DE2"/>
     <mergeCell ref="CQ1:CX2"/>
     <mergeCell ref="CY2:CY3"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="AC2:AK2"/>
+    <mergeCell ref="R1:CP1"/>
+    <mergeCell ref="EK2:EO2"/>
+    <mergeCell ref="EG2:EJ2"/>
+    <mergeCell ref="Q2:Q3"/>
+    <mergeCell ref="AL2:AQ2"/>
+    <mergeCell ref="AR2:BN2"/>
+    <mergeCell ref="Y2:AB2"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <dataValidations count="5">
+  <dataValidations disablePrompts="1" count="6">
     <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="CZ4:DE9" xr:uid="{33A3F0C5-F619-42A1-AAC0-ED869F398878}">
       <formula1>"---,Có,Không"</formula1>
     </dataValidation>
@@ -2271,20 +2272,20 @@
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Suggest" prompt="Nội dung cần nhập dưới định dạng mm/dd/yyyy" sqref="BG4:BG7 BZ4 CS4:CS8 DS4 DU4 DW4 DY4 EA4 ED4:EG9 EJ4:EJ8 EK4:EK5" xr:uid="{AACB1CA1-555A-4718-AA10-85174558E785}">
       <formula1>AND(BG4&gt;=DATE(1900,1,1),BG4&lt;=DATE(3000,12,31))</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O5:O9" xr:uid="{03F58363-C6A5-4418-AE34-F16B9C26686B}">
+      <formula1>#REF!</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{03F58363-C6A5-4418-AE34-F16B9C26686B}">
-          <x14:formula1>
-            <xm:f>#REF!</xm:f>
-          </x14:formula1>
-          <xm:sqref>O5:O9</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4968C5B-9752-4485-B83B-64E1009BC4C6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>